--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Auto Post\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Soul Touch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071BB7F1-2582-4D51-B078-8CF7C00352AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C7ABD9-E72A-4CBD-AA4F-99AB07045FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5355" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,14 +50,7 @@
     <t>নোট</t>
   </si>
   <si>
-    <t>swert.jpg</t>
-  </si>
-  <si>
     <t>Image</t>
-  </si>
-  <si>
-    <t>তুমি একা নও। কেউ না কেউ এই মুহূর্তে তোমার মতোই অনুভব করছে। 💙
-#motivation #bangla</t>
   </si>
   <si>
     <t>Pending</t>
@@ -94,6 +87,12 @@
   </si>
   <si>
     <t>তোমার নিজের জন্য যেকোনো নোট</t>
+  </si>
+  <si>
+    <t>1.png</t>
+  </si>
+  <si>
+    <t>#relax #massage #stressrelief</t>
   </si>
 </sst>
 </file>
@@ -567,19 +566,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="4">
+        <v>46243.083333333336</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="4">
-        <v>46236.704861111109</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -789,10 +788,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -800,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -808,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -816,7 +815,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -824,7 +823,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -832,7 +831,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -840,7 +839,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -848,7 +847,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -856,7 +855,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Soul Touch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C7ABD9-E72A-4CBD-AA4F-99AB07045FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4E28BB-69F4-46F0-BAF0-4A4215C04A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5355" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="4">
-        <v>46243.083333333336</v>
+        <v>46243.090277777781</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Soul Touch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F4E28BB-69F4-46F0-BAF0-4A4215C04A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5415F94C-8282-4D65-B1FF-8ACC1B56039A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5355" yWindow="2310" windowWidth="21600" windowHeight="13170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -575,7 +575,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="4">
-        <v>46243.090277777781</v>
+        <v>46243.100694444445</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\Soul Touch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF22507-A699-42AD-A60B-C09DA1EC8282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFDA90C-29B2-4D86-957A-B4C5EECEDC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Content Calendar" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -659,9 +659,14 @@
       <c r="E3" s="6" t="n">
         <v>46244.8125</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1026405146928119</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -692,9 +692,14 @@
       <c r="E4" s="6" t="n">
         <v>46245.10416666666</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1026681843567116</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -725,9 +725,14 @@
       <c r="E5" s="6" t="n">
         <v>46245.8125</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1027228816845752</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -758,9 +758,14 @@
       <c r="E6" s="6" t="n">
         <v>46246.10416666666</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1027531970148770</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -791,9 +791,14 @@
       <c r="E7" s="6" t="n">
         <v>46246.8125</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1028115953423705</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -824,9 +824,14 @@
       <c r="E8" s="6" t="n">
         <v>46247.10416666666</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1028379293397371</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -857,9 +857,14 @@
       <c r="E9" s="6" t="n">
         <v>46247.8125</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1028962986672335</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -890,9 +890,14 @@
       <c r="E10" s="6" t="n">
         <v>46248.10416666666</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1029187959983171</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -923,9 +923,14 @@
       <c r="E11" s="6" t="n">
         <v>46248.8125</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1029796089922358</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -956,9 +956,14 @@
       <c r="E12" s="6" t="n">
         <v>46249.10416666666</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1030015003233800</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -989,9 +989,14 @@
       <c r="E13" s="6" t="n">
         <v>46249.8125</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1030682153167085</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1022,9 +1022,14 @@
       <c r="E14" s="6" t="n">
         <v>46250.10416666666</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1030953156473318</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1055,9 +1055,14 @@
       <c r="E15" s="6" t="n">
         <v>46250.8125</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1031534963081804</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1088,9 +1088,14 @@
       <c r="E16" s="6" t="n">
         <v>46251.10416666666</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1031800959721871</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1121,9 +1121,14 @@
       <c r="E17" s="6" t="n">
         <v>46251.8125</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1032396152995685</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2050,9 +2050,14 @@
       <c r="E50" s="6" t="n">
         <v>46252.02083333334</v>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1674115797664324</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1154,9 +1154,14 @@
       <c r="E18" s="6" t="n">
         <v>46252.10416666666</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1032654539636513</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2088,9 +2088,14 @@
       <c r="E51" s="6" t="n">
         <v>46252.6875</v>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2038802576746508</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1187,9 +1187,14 @@
       <c r="E19" s="6" t="n">
         <v>46252.8125</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1033216149580352</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2126,9 +2126,14 @@
       <c r="E52" s="6" t="n">
         <v>46252.91666666666</v>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1416685637021701</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2159,9 +2159,14 @@
       <c r="E53" s="6" t="n">
         <v>46253.02083333334</v>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1354067710227739</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1220,9 +1220,14 @@
       <c r="E20" s="6" t="n">
         <v>46253.10416666666</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1033513156217318</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2197,9 +2197,14 @@
       <c r="E54" s="6" t="n">
         <v>46253.6875</v>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2253234105438742</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1253,9 +1253,14 @@
       <c r="E21" s="6" t="n">
         <v>46253.8125</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1034082359493731</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2235,9 +2235,14 @@
       <c r="E55" s="6" t="n">
         <v>46253.91666666666</v>
       </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1584825859852287</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1286,9 +1286,14 @@
       <c r="E22" s="6" t="n">
         <v>46254.10416666666</v>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1034401256128508</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1319,9 +1319,14 @@
       <c r="E23" s="6" t="n">
         <v>46254.8125</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1034951199406847</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1352,9 +1352,14 @@
       <c r="E24" s="6" t="n">
         <v>46255.10416666666</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1035240202711280</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1399,9 +1399,14 @@
       <c r="E25" s="6" t="n">
         <v>46255.8125</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1035806522654648</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2335,9 +2335,14 @@
       <c r="E57" s="7" t="n">
         <v>46255.91666666666</v>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1772741007195377</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2368,9 +2368,14 @@
       <c r="E58" s="7" t="n">
         <v>46256.02083333334</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1667505184351170</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1432,9 +1432,14 @@
       <c r="E26" s="6" t="n">
         <v>46256.10416666666</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1036101809291786</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2406,9 +2406,14 @@
       <c r="E59" s="7" t="n">
         <v>46256.6875</v>
       </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1584574089871111</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1465,9 +1465,14 @@
       <c r="E27" s="6" t="n">
         <v>46256.8125</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1036671292568171</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2444,9 +2444,14 @@
       <c r="E60" s="7" t="n">
         <v>46256.91666666666</v>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2220141368718193</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2477,9 +2477,14 @@
       <c r="E61" s="7" t="n">
         <v>46257.02083333334</v>
       </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>28062969309990466</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1498,9 +1498,14 @@
       <c r="E28" s="6" t="n">
         <v>46257.10416666666</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1036928782542422</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2515,9 +2515,14 @@
       <c r="E62" s="7" t="n">
         <v>46257.6875</v>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1065783942953351</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1531,9 +1531,14 @@
       <c r="E29" s="6" t="n">
         <v>46257.8125</v>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1037505942484706</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2553,9 +2553,14 @@
       <c r="E63" s="7" t="n">
         <v>46257.91666666666</v>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1005683492493863</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2586,9 +2586,14 @@
       <c r="E64" s="7" t="n">
         <v>46258.02083333334</v>
       </c>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1834225084244077</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1564,9 +1564,14 @@
       <c r="E30" s="6" t="n">
         <v>46258.10416666666</v>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1037757005792933</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2624,9 +2624,14 @@
       <c r="E65" s="7" t="n">
         <v>46258.6875</v>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>4346015762325884</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1597,9 +1597,14 @@
       <c r="E31" s="6" t="n">
         <v>46258.8125</v>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1038324619069505</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2662,9 +2662,14 @@
       <c r="E66" s="7" t="n">
         <v>46258.91666666666</v>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1481618600393068</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2695,9 +2695,14 @@
       <c r="E67" s="7" t="n">
         <v>46259.02083333334</v>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1868592004114923</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1630,9 +1630,14 @@
       <c r="E32" s="6" t="n">
         <v>46259.10416666666</v>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1038593745709259</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2733,9 +2733,14 @@
       <c r="E68" s="7" t="n">
         <v>46259.6875</v>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2224354928343426</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1663,9 +1663,14 @@
       <c r="E33" s="6" t="n">
         <v>46259.8125</v>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1039164988985468</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2771,9 +2771,14 @@
       <c r="E69" s="7" t="n">
         <v>46259.91666666666</v>
       </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2509976559468714</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2804,9 +2804,14 @@
       <c r="E70" s="7" t="n">
         <v>46260.02083333334</v>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2861613057571124</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1696,9 +1696,14 @@
       <c r="E34" s="6" t="n">
         <v>46260.10416666666</v>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1039464045622229</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2842,9 +2842,14 @@
       <c r="E71" s="7" t="n">
         <v>46260.6875</v>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2471798389995888</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1729,9 +1729,14 @@
       <c r="E35" s="6" t="n">
         <v>46260.8125</v>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1040026348899332</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2880,9 +2880,14 @@
       <c r="E72" s="7" t="n">
         <v>46260.91666666666</v>
       </c>
-      <c r="F72" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2540457616393024</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1762,9 +1762,14 @@
       <c r="E36" s="6" t="n">
         <v>46261.10416666666</v>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1041046745463959</t>
         </is>
       </c>
     </row>
@@ -1790,9 +1795,14 @@
       <c r="E37" s="6" t="n">
         <v>46261.8125</v>
       </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1041046808797286</t>
         </is>
       </c>
     </row>
@@ -2913,9 +2923,14 @@
       <c r="E73" s="7" t="n">
         <v>46261.02083333334</v>
       </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1624200952561081</t>
         </is>
       </c>
     </row>
@@ -2941,9 +2956,14 @@
       <c r="E74" s="7" t="n">
         <v>46261.6875</v>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>997030193394231</t>
         </is>
       </c>
     </row>
@@ -2969,9 +2989,14 @@
       <c r="E75" s="7" t="n">
         <v>46261.91666666666</v>
       </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>4596755160567323</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3022,9 +3022,14 @@
       <c r="E76" s="7" t="n">
         <v>46262.02083333334</v>
       </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1044267761705173</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1828,9 +1828,14 @@
       <c r="E38" s="6" t="n">
         <v>46262.10416666666</v>
       </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1041129062122394</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3060,9 +3060,14 @@
       <c r="E77" s="7" t="n">
         <v>46262.6875</v>
       </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>918396864199120</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1861,9 +1861,14 @@
       <c r="E39" s="6" t="n">
         <v>46262.8125</v>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1041759025392731</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3098,9 +3098,14 @@
       <c r="E78" s="7" t="n">
         <v>46262.91666666666</v>
       </c>
-      <c r="F78" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1593545455756976</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3131,9 +3131,14 @@
       <c r="E79" s="7" t="n">
         <v>46263.02083333334</v>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1383272926703465</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1894,9 +1894,14 @@
       <c r="E40" s="6" t="n">
         <v>46263.10416666666</v>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1042022445366389</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3169,9 +3169,14 @@
       <c r="E80" s="7" t="n">
         <v>46263.6875</v>
       </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1365436009033748</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1927,9 +1927,14 @@
       <c r="E41" s="6" t="n">
         <v>46263.8125</v>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1042605421974758</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3207,9 +3207,14 @@
       <c r="E81" s="7" t="n">
         <v>46263.91666666666</v>
       </c>
-      <c r="F81" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1598441161721414</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3240,9 +3240,14 @@
       <c r="E82" s="7" t="n">
         <v>46264.02083333334</v>
       </c>
-      <c r="F82" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1069347785820009</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1960,9 +1960,14 @@
       <c r="E42" s="6" t="n">
         <v>46264.10416666666</v>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1042864128615554</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3278,9 +3278,14 @@
       <c r="E83" s="7" t="n">
         <v>46264.6875</v>
       </c>
-      <c r="F83" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>1378389757181508</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1993,9 +1993,14 @@
       <c r="E43" s="6" t="n">
         <v>46264.8125</v>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1043434598558507</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3316,9 +3316,14 @@
       <c r="E84" s="7" t="n">
         <v>46264.91666666666</v>
       </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>1381683010785953</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3349,9 +3349,14 @@
       <c r="E85" s="7" t="n">
         <v>46265.02083333334</v>
       </c>
-      <c r="F85" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1049433774729758</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2026,9 +2026,14 @@
       <c r="E44" s="6" t="n">
         <v>46265.10416666666</v>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1043694248532542</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3387,9 +3387,14 @@
       <c r="E86" s="7" t="n">
         <v>46265.6875</v>
       </c>
-      <c r="F86" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1085819370667713</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2059,9 +2059,14 @@
       <c r="E45" s="6" t="n">
         <v>46265.8125</v>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1044249701810330</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3425,9 +3425,14 @@
       <c r="E87" s="7" t="n">
         <v>46265.91666666666</v>
       </c>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1465999558909567</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3458,9 +3458,14 @@
       <c r="E88" s="7" t="n">
         <v>46266.02083333334</v>
       </c>
-      <c r="F88" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>1011254311939097</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2092,9 +2092,14 @@
       <c r="E46" s="6" t="n">
         <v>46266.10416666666</v>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1044507391784561</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3496,9 +3496,14 @@
       <c r="E89" s="7" t="n">
         <v>46266.6875</v>
       </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1836341507797903</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2125,9 +2125,14 @@
       <c r="E47" s="6" t="n">
         <v>46266.8125</v>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1045084881726812</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3534,9 +3534,14 @@
       <c r="E90" s="7" t="n">
         <v>46266.91666666666</v>
       </c>
-      <c r="F90" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1744198683299921</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3567,9 +3567,14 @@
       <c r="E91" s="7" t="n">
         <v>46267.02083333334</v>
       </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2009966169716506</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2158,9 +2158,14 @@
       <c r="E48" s="6" t="n">
         <v>46267.10416666666</v>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1045357975032836</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3605,9 +3605,14 @@
       <c r="E92" s="7" t="n">
         <v>46267.6875</v>
       </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>1975936689732379</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2191,9 +2191,14 @@
       <c r="E49" s="6" t="n">
         <v>46267.8125</v>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1045924984976135</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3643,9 +3643,14 @@
       <c r="E93" s="7" t="n">
         <v>46267.91666666666</v>
       </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1058948093734156</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3676,9 +3676,14 @@
       <c r="E94" s="7" t="n">
         <v>46268.02083333334</v>
       </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2185126279098982</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3709,9 +3709,14 @@
       <c r="E95" s="7" t="n">
         <v>46268.6875</v>
       </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2955246538161289</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3742,9 +3742,14 @@
       <c r="E96" s="7" t="n">
         <v>46268.91666666666</v>
       </c>
-      <c r="F96" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1605242541130107</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3775,9 +3775,14 @@
       <c r="E97" s="7" t="n">
         <v>46269.02083333334</v>
       </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1017921614536304</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3808,9 +3808,14 @@
       <c r="E98" s="7" t="n">
         <v>46269.6875</v>
       </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1479028843987773</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3841,9 +3841,14 @@
       <c r="E99" s="7" t="n">
         <v>46269.91666666666</v>
       </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1422440703091293</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3874,9 +3874,14 @@
       <c r="E100" s="7" t="n">
         <v>46270.02083333334</v>
       </c>
-      <c r="F100" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1040861245443708</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3907,9 +3907,14 @@
       <c r="E101" s="7" t="n">
         <v>46270.6875</v>
       </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1734754581077896</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3940,9 +3940,14 @@
       <c r="E102" s="7" t="n">
         <v>46270.91666666666</v>
       </c>
-      <c r="F102" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1732172998050074</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3973,9 +3973,14 @@
       <c r="E103" s="7" t="n">
         <v>46271.02083333334</v>
       </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>1426538919364685</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4006,9 +4006,14 @@
       <c r="E104" s="7" t="n">
         <v>46271.6875</v>
       </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2985310268468228</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4039,9 +4039,14 @@
       <c r="E105" s="7" t="n">
         <v>46271.91666666666</v>
       </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1384289776563006</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4072,9 +4072,14 @@
       <c r="E106" s="7" t="n">
         <v>46272.02083333334</v>
       </c>
-      <c r="F106" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>1874338563528502</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4105,9 +4105,14 @@
       <c r="E107" s="7" t="n">
         <v>46272.6875</v>
       </c>
-      <c r="F107" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2140726650175356</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4138,9 +4138,14 @@
       <c r="E108" s="7" t="n">
         <v>46272.91666666666</v>
       </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>1047581298174304</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4171,9 +4171,14 @@
       <c r="E109" s="7" t="n">
         <v>46273.02083333334</v>
       </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2286131615505505</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4204,9 +4204,14 @@
       <c r="E110" s="7" t="n">
         <v>46273.6875</v>
       </c>
-      <c r="F110" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>1249319750651941</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4237,9 +4237,14 @@
       <c r="E111" s="7" t="n">
         <v>46273.91666666666</v>
       </c>
-      <c r="F111" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F111" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1641627674052771</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4270,9 +4270,14 @@
       <c r="E112" s="7" t="n">
         <v>46274.02083333334</v>
       </c>
-      <c r="F112" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F112" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2497909160706679</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4303,9 +4303,14 @@
       <c r="E113" s="7" t="n">
         <v>46274.6875</v>
       </c>
-      <c r="F113" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F113" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>28247151701609335</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4336,9 +4336,14 @@
       <c r="E114" s="7" t="n">
         <v>46274.91666666666</v>
       </c>
-      <c r="F114" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F114" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>4635650309998772</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4369,9 +4369,14 @@
       <c r="E115" s="7" t="n">
         <v>46275.02083333334</v>
       </c>
-      <c r="F115" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F115" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2072601273615273</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4402,9 +4402,14 @@
       <c r="E116" s="7" t="n">
         <v>46275.6875</v>
       </c>
-      <c r="F116" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F116" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2805979619771961</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4435,9 +4435,14 @@
       <c r="E117" s="7" t="n">
         <v>46275.91666666666</v>
       </c>
-      <c r="F117" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F117" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>28619177437718786</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4468,9 +4468,14 @@
       <c r="E118" s="7" t="n">
         <v>46276.02083333334</v>
       </c>
-      <c r="F118" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F118" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>1102945615755504</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4501,9 +4501,14 @@
       <c r="E119" s="7" t="n">
         <v>46276.6875</v>
       </c>
-      <c r="F119" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F119" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>1099572659112075</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4534,9 +4534,14 @@
       <c r="E120" s="7" t="n">
         <v>46276.91666666666</v>
       </c>
-      <c r="F120" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F120" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>1115138627861359</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4567,9 +4567,14 @@
       <c r="E121" s="7" t="n">
         <v>46277.02083333334</v>
       </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F121" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1380554850827845</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4600,9 +4600,14 @@
       <c r="E122" s="7" t="n">
         <v>46277.6875</v>
       </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>1090933796770552</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4633,9 +4633,14 @@
       <c r="E123" s="7" t="n">
         <v>46277.91666666666</v>
       </c>
-      <c r="F123" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F123" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>1638346954505582</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4666,9 +4666,14 @@
       <c r="E124" s="7" t="n">
         <v>46278.02083333334</v>
       </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F124" s="10" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>1630550415100985</t>
         </is>
       </c>
     </row>
